--- a/S_数据表/EquipSuitProperty_Template.xlsx
+++ b/S_数据表/EquipSuitProperty_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WeijingGame\S_数据表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\YongShi\S_数据表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACEE0E5-B35F-4B3E-808F-7E1BEEA04099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82D498B-CBBF-4BCC-87CA-020D01BFA3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -677,9 +677,6 @@
     <t>Enhanced Damage+5%,critical+5%</t>
   </si>
   <si>
-    <t>DEF+3-6，RES+3-6</t>
-  </si>
-  <si>
     <t>EquipSuitName_EN</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -688,23 +685,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Attack+10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击+400</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
@@ -887,6 +867,146 @@
   <si>
     <t>血量+1440 血量上限+6%</t>
     <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>不朽套装1_3</t>
+  </si>
+  <si>
+    <t>不朽套装2_2</t>
+  </si>
+  <si>
+    <t>不朽套装2_3</t>
+  </si>
+  <si>
+    <t>不朽套装2_4</t>
+  </si>
+  <si>
+    <t>不朽套装3_2</t>
+  </si>
+  <si>
+    <t>不朽套装4_3</t>
+  </si>
+  <si>
+    <t>攻击+180 命中率+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack+180 Rating +5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack+520</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack+120 critical+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+640</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack+640</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+180 暴击+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack+180 Critical+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>物防：120-180  受到伤害减免5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔防：120-180  伤害加成5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF+120-180，Damage reduction+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF+80-120 Damage reduction+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enhanced Damage+5% critical+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enhanced Damage+5% Critical+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack+400</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF+50-80，Damage reduction+5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK:80-80, PhyPen +1%</t>
+  </si>
+  <si>
+    <t>SP +80, MagPen +1%</t>
+  </si>
+  <si>
+    <t>HP +360, MaxHP +1%</t>
+  </si>
+  <si>
+    <t>ATK:120-120, PhyPen +2%</t>
+  </si>
+  <si>
+    <t>SP +120, MagPen +2%</t>
+  </si>
+  <si>
+    <t>HP +540, MaxHP +2%</t>
+  </si>
+  <si>
+    <t>ATK:160-160, PhyPen +3%</t>
+  </si>
+  <si>
+    <t>SP +160, MagPen +3%</t>
+  </si>
+  <si>
+    <t>HP +720, MaxHP +3%</t>
+  </si>
+  <si>
+    <t>ATK:200-200, PhyPen +4%</t>
+  </si>
+  <si>
+    <t>SP +200, MagPen +4%</t>
+  </si>
+  <si>
+    <t>HP +900, MaxHP +4%</t>
+  </si>
+  <si>
+    <t>ATK:240-240, PhyPen +5%</t>
+  </si>
+  <si>
+    <t>SP +240, MagPen +5%</t>
+  </si>
+  <si>
+    <t>HP +1080, MaxHP +5%</t>
+  </si>
+  <si>
+    <t>ATK:320-320, PhyPen +6%</t>
+  </si>
+  <si>
+    <t>SP +320, MagPen +6%</t>
+  </si>
+  <si>
+    <t>HP +1440, MaxHP +6%</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X105"/>
+  <dimension ref="A1:X111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
@@ -1909,13 +2029,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>22</v>
@@ -7185,10 +7305,10 @@
         <v>156</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="F77" s="11">
         <v>0</v>
@@ -7261,8 +7381,8 @@
       <c r="D78" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>169</v>
+      <c r="E78" s="15" t="s">
+        <v>255</v>
       </c>
       <c r="F78" s="11">
         <v>0</v>
@@ -7335,8 +7455,8 @@
       <c r="D79" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>186</v>
+      <c r="E79" s="15" t="s">
+        <v>254</v>
       </c>
       <c r="F79" s="11">
         <v>0</v>
@@ -7407,10 +7527,10 @@
         <v>156</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>257</v>
       </c>
       <c r="F80" s="11">
         <v>0</v>
@@ -7481,10 +7601,10 @@
         <v>156</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F81" s="11">
         <v>0</v>
@@ -7546,7 +7666,6 @@
     </row>
     <row r="82" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="7">
-        <f>A76+100</f>
         <v>15711</v>
       </c>
       <c r="B82" s="11" t="s">
@@ -7556,7 +7675,7 @@
         <v>156</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>158</v>
@@ -7621,7 +7740,6 @@
     </row>
     <row r="83" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="7">
-        <f t="shared" ref="A83:A87" si="0">A77+100</f>
         <v>15721</v>
       </c>
       <c r="B83" s="11" t="s">
@@ -7631,10 +7749,10 @@
         <v>156</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="F83" s="11">
         <v>0</v>
@@ -7696,7 +7814,6 @@
     </row>
     <row r="84" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="7">
-        <f t="shared" si="0"/>
         <v>15722</v>
       </c>
       <c r="B84" s="11" t="s">
@@ -7706,10 +7823,10 @@
         <v>156</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>169</v>
+        <v>227</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>244</v>
       </c>
       <c r="F84" s="11">
         <v>0</v>
@@ -7771,7 +7888,6 @@
     </row>
     <row r="85" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="7">
-        <f t="shared" si="0"/>
         <v>15723</v>
       </c>
       <c r="B85" s="11" t="s">
@@ -7783,8 +7899,8 @@
       <c r="D85" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="E85" s="7" t="s">
-        <v>186</v>
+      <c r="E85" s="15" t="s">
+        <v>253</v>
       </c>
       <c r="F85" s="11">
         <v>0</v>
@@ -7846,7 +7962,6 @@
     </row>
     <row r="86" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="7">
-        <f t="shared" si="0"/>
         <v>15731</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -7856,10 +7971,10 @@
         <v>156</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>187</v>
+        <v>224</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>252</v>
       </c>
       <c r="F86" s="11">
         <v>0</v>
@@ -7921,7 +8036,6 @@
     </row>
     <row r="87" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="7">
-        <f t="shared" si="0"/>
         <v>15741</v>
       </c>
       <c r="B87" s="11" t="s">
@@ -7931,10 +8045,10 @@
         <v>156</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F87" s="11">
         <v>0</v>
@@ -7996,18 +8110,20 @@
     </row>
     <row r="88" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="7">
-        <v>16011</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>195</v>
+        <v>15811</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>235</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E88" s="7"/>
+        <v>241</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>242</v>
+      </c>
       <c r="F88" s="11">
         <v>0</v>
       </c>
@@ -8015,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="12">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I88" s="12">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="J88" s="12">
         <v>0</v>
@@ -8042,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R88" s="12">
         <v>0</v>
@@ -8062,24 +8178,26 @@
       <c r="W88" s="7">
         <v>0</v>
       </c>
-      <c r="X88" s="15" t="s">
-        <v>199</v>
+      <c r="X88" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="7">
-        <v>16012</v>
-      </c>
-      <c r="B89" s="17" t="s">
-        <v>195</v>
+        <v>15821</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="E89" s="7"/>
+        <v>245</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>246</v>
+      </c>
       <c r="F89" s="11">
         <v>0</v>
       </c>
@@ -8090,13 +8208,13 @@
         <v>0</v>
       </c>
       <c r="I89" s="12">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="J89" s="12">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K89" s="12">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L89" s="12">
         <v>0</v>
@@ -8134,35 +8252,37 @@
       <c r="W89" s="7">
         <v>0</v>
       </c>
-      <c r="X89" s="15" t="s">
-        <v>200</v>
+      <c r="X89" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="7">
-        <v>16013</v>
-      </c>
-      <c r="B90" s="17" t="s">
-        <v>195</v>
+        <v>15822</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>237</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="E90" s="7"/>
+        <v>247</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>248</v>
+      </c>
       <c r="F90" s="11">
         <v>0</v>
       </c>
       <c r="G90" s="12">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H90" s="12">
         <v>0</v>
       </c>
       <c r="I90" s="12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J90" s="12">
         <v>0</v>
@@ -8183,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q90" s="12">
         <v>0</v>
@@ -8206,24 +8326,26 @@
       <c r="W90" s="7">
         <v>0</v>
       </c>
-      <c r="X90" s="15" t="s">
-        <v>198</v>
+      <c r="X90" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="7">
-        <v>16021</v>
-      </c>
-      <c r="B91" s="17" t="s">
-        <v>195</v>
+        <v>15823</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>238</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D91" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="E91" s="7"/>
+      <c r="D91" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>186</v>
+      </c>
       <c r="F91" s="11">
         <v>0</v>
       </c>
@@ -8231,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="12">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I91" s="12">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J91" s="12">
         <v>0</v>
@@ -8255,7 +8377,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q91" s="12">
         <v>0</v>
@@ -8264,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T91" s="12">
         <v>0</v>
@@ -8278,24 +8400,26 @@
       <c r="W91" s="7">
         <v>0</v>
       </c>
-      <c r="X91" s="15" t="s">
-        <v>201</v>
+      <c r="X91" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="7">
-        <v>16022</v>
-      </c>
-      <c r="B92" s="17" t="s">
-        <v>195</v>
+        <v>15831</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="E92" s="7"/>
+        <v>249</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>251</v>
+      </c>
       <c r="F92" s="11">
         <v>0</v>
       </c>
@@ -8309,16 +8433,16 @@
         <v>0</v>
       </c>
       <c r="J92" s="12">
+        <v>0</v>
+      </c>
+      <c r="K92" s="12">
+        <v>0</v>
+      </c>
+      <c r="L92" s="12">
         <v>120</v>
       </c>
-      <c r="K92" s="12">
-        <v>120</v>
-      </c>
-      <c r="L92" s="12">
-        <v>0</v>
-      </c>
       <c r="M92" s="12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N92" s="12">
         <v>0</v>
@@ -8339,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="T92" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="U92" s="13">
         <v>0</v>
@@ -8350,29 +8474,31 @@
       <c r="W92" s="7">
         <v>0</v>
       </c>
-      <c r="X92" s="15" t="s">
-        <v>202</v>
+      <c r="X92" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="7">
-        <v>16023</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>195</v>
+        <v>15841</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="E93" s="7"/>
+        <v>250</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>192</v>
+      </c>
       <c r="F93" s="11">
         <v>0</v>
       </c>
       <c r="G93" s="12">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H93" s="12">
         <v>0</v>
@@ -8393,10 +8519,10 @@
         <v>0</v>
       </c>
       <c r="N93" s="12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O93" s="12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="P93" s="12">
         <v>0</v>
@@ -8408,7 +8534,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T93" s="12">
         <v>0</v>
@@ -8422,24 +8548,26 @@
       <c r="W93" s="7">
         <v>0</v>
       </c>
-      <c r="X93" s="15" t="s">
-        <v>203</v>
+      <c r="X93" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="7">
-        <v>16031</v>
+        <v>16011</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="E94" s="7"/>
+        <v>194</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>258</v>
+      </c>
       <c r="F94" s="11">
         <v>0</v>
       </c>
@@ -8447,10 +8575,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="12">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="I94" s="12">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="J94" s="12">
         <v>0</v>
@@ -8495,23 +8623,25 @@
         <v>0</v>
       </c>
       <c r="X94" s="15" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="7">
-        <v>16032</v>
+        <v>16012</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="E95" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>259</v>
+      </c>
       <c r="F95" s="11">
         <v>0</v>
       </c>
@@ -8525,10 +8655,10 @@
         <v>0</v>
       </c>
       <c r="J95" s="12">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="K95" s="12">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="L95" s="12">
         <v>0</v>
@@ -8567,28 +8697,30 @@
         <v>0</v>
       </c>
       <c r="X95" s="15" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="7">
-        <v>16033</v>
+        <v>16013</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="E96" s="7"/>
+        <v>214</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>260</v>
+      </c>
       <c r="F96" s="11">
         <v>0</v>
       </c>
       <c r="G96" s="12">
-        <v>720</v>
+        <v>360</v>
       </c>
       <c r="H96" s="12">
         <v>0</v>
@@ -8639,23 +8771,25 @@
         <v>0</v>
       </c>
       <c r="X96" s="15" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="7">
-        <v>16041</v>
+        <v>16021</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="E97" s="7"/>
+        <v>211</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>261</v>
+      </c>
       <c r="F97" s="11">
         <v>0</v>
       </c>
@@ -8663,10 +8797,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="12">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="I97" s="12">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="J97" s="12">
         <v>0</v>
@@ -8711,23 +8845,25 @@
         <v>0</v>
       </c>
       <c r="X97" s="15" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="7">
-        <v>16042</v>
+        <v>16022</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="E98" s="7"/>
+        <v>212</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>262</v>
+      </c>
       <c r="F98" s="11">
         <v>0</v>
       </c>
@@ -8741,70 +8877,72 @@
         <v>0</v>
       </c>
       <c r="J98" s="12">
+        <v>120</v>
+      </c>
+      <c r="K98" s="12">
+        <v>120</v>
+      </c>
+      <c r="L98" s="12">
+        <v>0</v>
+      </c>
+      <c r="M98" s="12">
+        <v>0</v>
+      </c>
+      <c r="N98" s="12">
+        <v>0</v>
+      </c>
+      <c r="O98" s="12">
+        <v>0</v>
+      </c>
+      <c r="P98" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="12">
+        <v>0</v>
+      </c>
+      <c r="R98" s="12">
+        <v>0</v>
+      </c>
+      <c r="S98" s="12">
+        <v>0</v>
+      </c>
+      <c r="T98" s="12">
+        <v>0</v>
+      </c>
+      <c r="U98" s="13">
+        <v>0</v>
+      </c>
+      <c r="V98" s="7">
+        <v>0</v>
+      </c>
+      <c r="W98" s="7">
+        <v>0</v>
+      </c>
+      <c r="X98" s="15" t="s">
         <v>200</v>
-      </c>
-      <c r="K98" s="12">
-        <v>200</v>
-      </c>
-      <c r="L98" s="12">
-        <v>0</v>
-      </c>
-      <c r="M98" s="12">
-        <v>0</v>
-      </c>
-      <c r="N98" s="12">
-        <v>0</v>
-      </c>
-      <c r="O98" s="12">
-        <v>0</v>
-      </c>
-      <c r="P98" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="12">
-        <v>0</v>
-      </c>
-      <c r="R98" s="12">
-        <v>0</v>
-      </c>
-      <c r="S98" s="12">
-        <v>0</v>
-      </c>
-      <c r="T98" s="12">
-        <v>0</v>
-      </c>
-      <c r="U98" s="13">
-        <v>0</v>
-      </c>
-      <c r="V98" s="7">
-        <v>0</v>
-      </c>
-      <c r="W98" s="7">
-        <v>0</v>
-      </c>
-      <c r="X98" s="15" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="7">
-        <v>16043</v>
+        <v>16023</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="E99" s="7"/>
+        <v>213</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>263</v>
+      </c>
       <c r="F99" s="11">
         <v>0</v>
       </c>
       <c r="G99" s="12">
-        <v>900</v>
+        <v>540</v>
       </c>
       <c r="H99" s="12">
         <v>0</v>
@@ -8855,23 +8993,25 @@
         <v>0</v>
       </c>
       <c r="X99" s="15" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="7">
-        <v>16051</v>
+        <v>16031</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="E100" s="7"/>
+        <v>215</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="F100" s="11">
         <v>0</v>
       </c>
@@ -8879,10 +9019,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="12">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="I100" s="12">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="J100" s="12">
         <v>0</v>
@@ -8927,23 +9067,25 @@
         <v>0</v>
       </c>
       <c r="X100" s="15" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="7">
-        <v>16052</v>
+        <v>16032</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="E101" s="7"/>
+        <v>216</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>265</v>
+      </c>
       <c r="F101" s="11">
         <v>0</v>
       </c>
@@ -8957,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="J101" s="12">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="K101" s="12">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="L101" s="12">
         <v>0</v>
@@ -8999,28 +9141,30 @@
         <v>0</v>
       </c>
       <c r="X101" s="15" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="7">
-        <v>16053</v>
+        <v>16033</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="E102" s="7"/>
+        <v>217</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>266</v>
+      </c>
       <c r="F102" s="11">
         <v>0</v>
       </c>
       <c r="G102" s="12">
-        <v>1080</v>
+        <v>720</v>
       </c>
       <c r="H102" s="12">
         <v>0</v>
@@ -9071,23 +9215,25 @@
         <v>0</v>
       </c>
       <c r="X102" s="15" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="7">
-        <v>16061</v>
+        <v>16041</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="E103" s="7"/>
+        <v>218</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>267</v>
+      </c>
       <c r="F103" s="11">
         <v>0</v>
       </c>
@@ -9095,10 +9241,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="12">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I103" s="12">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="J103" s="12">
         <v>0</v>
@@ -9143,23 +9289,25 @@
         <v>0</v>
       </c>
       <c r="X103" s="15" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="7">
-        <v>16062</v>
+        <v>16042</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="E104" s="7"/>
+        <v>219</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>268</v>
+      </c>
       <c r="F104" s="11">
         <v>0</v>
       </c>
@@ -9173,10 +9321,10 @@
         <v>0</v>
       </c>
       <c r="J104" s="12">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="K104" s="12">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="L104" s="12">
         <v>0</v>
@@ -9215,79 +9363,525 @@
         <v>0</v>
       </c>
       <c r="X104" s="15" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="7">
-        <v>16063</v>
+        <v>16043</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>156</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="E105" s="7"/>
+        <v>220</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>269</v>
+      </c>
       <c r="F105" s="11">
         <v>0</v>
       </c>
       <c r="G105" s="12">
+        <v>900</v>
+      </c>
+      <c r="H105" s="12">
+        <v>0</v>
+      </c>
+      <c r="I105" s="12">
+        <v>0</v>
+      </c>
+      <c r="J105" s="12">
+        <v>0</v>
+      </c>
+      <c r="K105" s="12">
+        <v>0</v>
+      </c>
+      <c r="L105" s="12">
+        <v>0</v>
+      </c>
+      <c r="M105" s="12">
+        <v>0</v>
+      </c>
+      <c r="N105" s="12">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12">
+        <v>0</v>
+      </c>
+      <c r="P105" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="12">
+        <v>0</v>
+      </c>
+      <c r="R105" s="12">
+        <v>0</v>
+      </c>
+      <c r="S105" s="12">
+        <v>0</v>
+      </c>
+      <c r="T105" s="12">
+        <v>0</v>
+      </c>
+      <c r="U105" s="13">
+        <v>0</v>
+      </c>
+      <c r="V105" s="7">
+        <v>0</v>
+      </c>
+      <c r="W105" s="7">
+        <v>0</v>
+      </c>
+      <c r="X105" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A106" s="7">
+        <v>16051</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D106" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="F106" s="11">
+        <v>0</v>
+      </c>
+      <c r="G106" s="12">
+        <v>0</v>
+      </c>
+      <c r="H106" s="12">
+        <v>240</v>
+      </c>
+      <c r="I106" s="12">
+        <v>240</v>
+      </c>
+      <c r="J106" s="12">
+        <v>0</v>
+      </c>
+      <c r="K106" s="12">
+        <v>0</v>
+      </c>
+      <c r="L106" s="12">
+        <v>0</v>
+      </c>
+      <c r="M106" s="12">
+        <v>0</v>
+      </c>
+      <c r="N106" s="12">
+        <v>0</v>
+      </c>
+      <c r="O106" s="12">
+        <v>0</v>
+      </c>
+      <c r="P106" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="12">
+        <v>0</v>
+      </c>
+      <c r="R106" s="12">
+        <v>0</v>
+      </c>
+      <c r="S106" s="12">
+        <v>0</v>
+      </c>
+      <c r="T106" s="12">
+        <v>0</v>
+      </c>
+      <c r="U106" s="13">
+        <v>0</v>
+      </c>
+      <c r="V106" s="7">
+        <v>0</v>
+      </c>
+      <c r="W106" s="7">
+        <v>0</v>
+      </c>
+      <c r="X106" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A107" s="7">
+        <v>16052</v>
+      </c>
+      <c r="B107" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D107" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="F107" s="11">
+        <v>0</v>
+      </c>
+      <c r="G107" s="12">
+        <v>0</v>
+      </c>
+      <c r="H107" s="12">
+        <v>0</v>
+      </c>
+      <c r="I107" s="12">
+        <v>0</v>
+      </c>
+      <c r="J107" s="12">
+        <v>240</v>
+      </c>
+      <c r="K107" s="12">
+        <v>240</v>
+      </c>
+      <c r="L107" s="12">
+        <v>0</v>
+      </c>
+      <c r="M107" s="12">
+        <v>0</v>
+      </c>
+      <c r="N107" s="12">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12">
+        <v>0</v>
+      </c>
+      <c r="P107" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="12">
+        <v>0</v>
+      </c>
+      <c r="R107" s="12">
+        <v>0</v>
+      </c>
+      <c r="S107" s="12">
+        <v>0</v>
+      </c>
+      <c r="T107" s="12">
+        <v>0</v>
+      </c>
+      <c r="U107" s="13">
+        <v>0</v>
+      </c>
+      <c r="V107" s="7">
+        <v>0</v>
+      </c>
+      <c r="W107" s="7">
+        <v>0</v>
+      </c>
+      <c r="X107" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A108" s="7">
+        <v>16053</v>
+      </c>
+      <c r="B108" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D108" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="F108" s="11">
+        <v>0</v>
+      </c>
+      <c r="G108" s="12">
+        <v>1080</v>
+      </c>
+      <c r="H108" s="12">
+        <v>0</v>
+      </c>
+      <c r="I108" s="12">
+        <v>0</v>
+      </c>
+      <c r="J108" s="12">
+        <v>0</v>
+      </c>
+      <c r="K108" s="12">
+        <v>0</v>
+      </c>
+      <c r="L108" s="12">
+        <v>0</v>
+      </c>
+      <c r="M108" s="12">
+        <v>0</v>
+      </c>
+      <c r="N108" s="12">
+        <v>0</v>
+      </c>
+      <c r="O108" s="12">
+        <v>0</v>
+      </c>
+      <c r="P108" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="12">
+        <v>0</v>
+      </c>
+      <c r="R108" s="12">
+        <v>0</v>
+      </c>
+      <c r="S108" s="12">
+        <v>0</v>
+      </c>
+      <c r="T108" s="12">
+        <v>0</v>
+      </c>
+      <c r="U108" s="13">
+        <v>0</v>
+      </c>
+      <c r="V108" s="7">
+        <v>0</v>
+      </c>
+      <c r="W108" s="7">
+        <v>0</v>
+      </c>
+      <c r="X108" s="15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A109" s="7">
+        <v>16061</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D109" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F109" s="11">
+        <v>0</v>
+      </c>
+      <c r="G109" s="12">
+        <v>0</v>
+      </c>
+      <c r="H109" s="12">
+        <v>320</v>
+      </c>
+      <c r="I109" s="12">
+        <v>320</v>
+      </c>
+      <c r="J109" s="12">
+        <v>0</v>
+      </c>
+      <c r="K109" s="12">
+        <v>0</v>
+      </c>
+      <c r="L109" s="12">
+        <v>0</v>
+      </c>
+      <c r="M109" s="12">
+        <v>0</v>
+      </c>
+      <c r="N109" s="12">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12">
+        <v>0</v>
+      </c>
+      <c r="P109" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="12">
+        <v>0</v>
+      </c>
+      <c r="R109" s="12">
+        <v>0</v>
+      </c>
+      <c r="S109" s="12">
+        <v>0</v>
+      </c>
+      <c r="T109" s="12">
+        <v>0</v>
+      </c>
+      <c r="U109" s="13">
+        <v>0</v>
+      </c>
+      <c r="V109" s="7">
+        <v>0</v>
+      </c>
+      <c r="W109" s="7">
+        <v>0</v>
+      </c>
+      <c r="X109" s="15" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="7">
+        <v>16062</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D110" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F110" s="11">
+        <v>0</v>
+      </c>
+      <c r="G110" s="12">
+        <v>0</v>
+      </c>
+      <c r="H110" s="12">
+        <v>0</v>
+      </c>
+      <c r="I110" s="12">
+        <v>0</v>
+      </c>
+      <c r="J110" s="12">
+        <v>320</v>
+      </c>
+      <c r="K110" s="12">
+        <v>320</v>
+      </c>
+      <c r="L110" s="12">
+        <v>0</v>
+      </c>
+      <c r="M110" s="12">
+        <v>0</v>
+      </c>
+      <c r="N110" s="12">
+        <v>0</v>
+      </c>
+      <c r="O110" s="12">
+        <v>0</v>
+      </c>
+      <c r="P110" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="12">
+        <v>0</v>
+      </c>
+      <c r="R110" s="12">
+        <v>0</v>
+      </c>
+      <c r="S110" s="12">
+        <v>0</v>
+      </c>
+      <c r="T110" s="12">
+        <v>0</v>
+      </c>
+      <c r="U110" s="13">
+        <v>0</v>
+      </c>
+      <c r="V110" s="7">
+        <v>0</v>
+      </c>
+      <c r="W110" s="7">
+        <v>0</v>
+      </c>
+      <c r="X110" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A111" s="7">
+        <v>16063</v>
+      </c>
+      <c r="B111" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D111" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F111" s="11">
+        <v>0</v>
+      </c>
+      <c r="G111" s="12">
         <v>1440</v>
       </c>
-      <c r="H105" s="12">
-        <v>0</v>
-      </c>
-      <c r="I105" s="12">
-        <v>0</v>
-      </c>
-      <c r="J105" s="12">
-        <v>0</v>
-      </c>
-      <c r="K105" s="12">
-        <v>0</v>
-      </c>
-      <c r="L105" s="12">
-        <v>0</v>
-      </c>
-      <c r="M105" s="12">
-        <v>0</v>
-      </c>
-      <c r="N105" s="12">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12">
-        <v>0</v>
-      </c>
-      <c r="P105" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="12">
-        <v>0</v>
-      </c>
-      <c r="R105" s="12">
-        <v>0</v>
-      </c>
-      <c r="S105" s="12">
-        <v>0</v>
-      </c>
-      <c r="T105" s="12">
-        <v>0</v>
-      </c>
-      <c r="U105" s="13">
-        <v>0</v>
-      </c>
-      <c r="V105" s="7">
-        <v>0</v>
-      </c>
-      <c r="W105" s="7">
-        <v>0</v>
-      </c>
-      <c r="X105" s="15" t="s">
-        <v>233</v>
+      <c r="H111" s="12">
+        <v>0</v>
+      </c>
+      <c r="I111" s="12">
+        <v>0</v>
+      </c>
+      <c r="J111" s="12">
+        <v>0</v>
+      </c>
+      <c r="K111" s="12">
+        <v>0</v>
+      </c>
+      <c r="L111" s="12">
+        <v>0</v>
+      </c>
+      <c r="M111" s="12">
+        <v>0</v>
+      </c>
+      <c r="N111" s="12">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12">
+        <v>0</v>
+      </c>
+      <c r="P111" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="12">
+        <v>0</v>
+      </c>
+      <c r="R111" s="12">
+        <v>0</v>
+      </c>
+      <c r="S111" s="12">
+        <v>0</v>
+      </c>
+      <c r="T111" s="12">
+        <v>0</v>
+      </c>
+      <c r="U111" s="13">
+        <v>0</v>
+      </c>
+      <c r="V111" s="7">
+        <v>0</v>
+      </c>
+      <c r="W111" s="7">
+        <v>0</v>
+      </c>
+      <c r="X111" s="15" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
